--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0003T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.45320040759935</v>
+        <v>7.711145066234895</v>
       </c>
       <c r="D2" t="n">
-        <v>35.18272438901484</v>
+        <v>5.717192713214913</v>
       </c>
       <c r="E2" t="n">
-        <v>13.17042876436517</v>
+        <v>2.140194674209339</v>
       </c>
       <c r="F2" t="n">
-        <v>11.96937022398823</v>
+        <v>1.945022661398087</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.73027035311332</v>
+        <v>5.481168932380915</v>
       </c>
       <c r="D3" t="n">
-        <v>33.38634797015731</v>
+        <v>5.425281545150563</v>
       </c>
       <c r="E3" t="n">
-        <v>13.17042876436517</v>
+        <v>2.140194674209339</v>
       </c>
       <c r="F3" t="n">
-        <v>11.96937022398823</v>
+        <v>1.945022661398087</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.49635945688212</v>
+        <v>6.255658411743345</v>
       </c>
       <c r="D4" t="n">
-        <v>35.52370784576728</v>
+        <v>5.772602524937184</v>
       </c>
       <c r="E4" t="n">
-        <v>13.17042876436517</v>
+        <v>2.140194674209339</v>
       </c>
       <c r="F4" t="n">
-        <v>11.96937022398823</v>
+        <v>1.945022661398087</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.06907937715251</v>
+        <v>4.236225398787283</v>
       </c>
       <c r="D5" t="n">
-        <v>26.44171756118973</v>
+        <v>4.296779103693331</v>
       </c>
       <c r="E5" t="n">
-        <v>13.17042876436517</v>
+        <v>2.140194674209339</v>
       </c>
       <c r="F5" t="n">
-        <v>11.96937022398823</v>
+        <v>1.945022661398087</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.79503133500761</v>
+        <v>2.404192591938737</v>
       </c>
       <c r="D6" t="n">
-        <v>16.5255277308576</v>
+        <v>2.68539825626436</v>
       </c>
       <c r="E6" t="n">
-        <v>13.17042876436517</v>
+        <v>2.140194674209339</v>
       </c>
       <c r="F6" t="n">
-        <v>11.96937022398823</v>
+        <v>1.945022661398087</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>35.29257992578457</v>
+        <v>5.735044237939992</v>
       </c>
       <c r="D7" t="n">
-        <v>36.58341272822577</v>
+        <v>5.944804568336688</v>
       </c>
       <c r="E7" t="n">
-        <v>13.17042876436517</v>
+        <v>2.140194674209339</v>
       </c>
       <c r="F7" t="n">
-        <v>11.96937022398823</v>
+        <v>1.945022661398087</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.29398659618598</v>
+        <v>7.197772821880222</v>
       </c>
       <c r="D8" t="n">
-        <v>44.96488868472265</v>
+        <v>7.306794411267431</v>
       </c>
       <c r="E8" t="n">
-        <v>13.17042876436517</v>
+        <v>2.140194674209339</v>
       </c>
       <c r="F8" t="n">
-        <v>11.96937022398823</v>
+        <v>1.945022661398087</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.76488149108962</v>
+        <v>6.299293242302064</v>
       </c>
       <c r="D9" t="n">
-        <v>40.11425830052477</v>
+        <v>6.518566973835275</v>
       </c>
       <c r="E9" t="n">
-        <v>13.17042876436517</v>
+        <v>2.140194674209339</v>
       </c>
       <c r="F9" t="n">
-        <v>11.96937022398823</v>
+        <v>1.945022661398087</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>22.80299032084287</v>
+        <v>3.705485927136967</v>
       </c>
       <c r="D10" t="n">
-        <v>22.62943936716782</v>
+        <v>3.677283897164771</v>
       </c>
       <c r="E10" t="n">
-        <v>13.17042876436517</v>
+        <v>2.140194674209339</v>
       </c>
       <c r="F10" t="n">
-        <v>11.96937022398823</v>
+        <v>1.945022661398087</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.38041103071236</v>
+        <v>2.661816792490759</v>
       </c>
       <c r="D11" t="n">
-        <v>16.42151404056628</v>
+        <v>2.66849603159202</v>
       </c>
       <c r="E11" t="n">
-        <v>13.17042876436517</v>
+        <v>2.140194674209339</v>
       </c>
       <c r="F11" t="n">
-        <v>11.96937022398823</v>
+        <v>1.945022661398087</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>2.952420137488473</v>
+        <v>0.4797682723418769</v>
       </c>
       <c r="D12" t="n">
-        <v>2.81883918771244</v>
+        <v>0.4580613680032716</v>
       </c>
       <c r="E12" t="n">
-        <v>13.17042876436517</v>
+        <v>2.140194674209339</v>
       </c>
       <c r="F12" t="n">
-        <v>11.96937022398823</v>
+        <v>1.945022661398087</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
